--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,12 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579429.0137228165</v>
+        <v>579429</v>
       </c>
       <c r="R3" t="n">
-        <v>6320002.404544913</v>
+        <v>6320002</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -879,19 +874,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3238-2021 artfynd.xlsx
+++ b/artfynd/A 3238-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>74604652</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
